--- a/data/base/Backlog_33.xlsx
+++ b/data/base/Backlog_33.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC68752-E461-4711-91A6-C93F8B27E6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2593CF-5BBC-4466-9277-A44BE47D924F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F7992F62-A5A5-4D5B-880A-726CB0342990}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F7992F62-A5A5-4D5B-880A-726CB0342990}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="1" r:id="rId1"/>
     <sheet name="SPN" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$K$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -298,7 +298,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -484,6 +484,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -660,7 +666,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -683,6 +689,20 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="19" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="19" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1112,73 +1132,73 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="7" t="s">
+    <row r="2" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="1">
-        <v>33</v>
-      </c>
-      <c r="E2" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F2" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G2" s="1">
+      <c r="C2" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="10">
+        <v>33</v>
+      </c>
+      <c r="E2" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F2" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G2" s="10">
         <v>22708</v>
       </c>
-      <c r="H2" s="9">
-        <v>46235</v>
-      </c>
-      <c r="I2" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="H2" s="13">
+        <v>46235</v>
+      </c>
+      <c r="I2" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="K2" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="1">
-        <v>33</v>
-      </c>
-      <c r="E3" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F3" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G3" s="1">
+      <c r="C3" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="10">
+        <v>33</v>
+      </c>
+      <c r="E3" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F3" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G3" s="10">
         <v>23225</v>
       </c>
-      <c r="H3" s="9">
-        <v>46235</v>
-      </c>
-      <c r="I3" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="H3" s="13">
+        <v>46235</v>
+      </c>
+      <c r="I3" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="10" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1217,73 +1237,73 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="7" t="s">
+    <row r="5" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="1">
-        <v>33</v>
-      </c>
-      <c r="E5" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F5" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G5" s="1">
+      <c r="C5" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="10">
+        <v>33</v>
+      </c>
+      <c r="E5" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F5" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G5" s="10">
         <v>22555</v>
       </c>
-      <c r="H5" s="9">
-        <v>46235</v>
-      </c>
-      <c r="I5" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J5" s="1" t="s">
+      <c r="H5" s="13">
+        <v>46235</v>
+      </c>
+      <c r="I5" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="K5" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="1">
-        <v>33</v>
-      </c>
-      <c r="E6" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F6" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="C6" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="10">
+        <v>33</v>
+      </c>
+      <c r="E6" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F6" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G6" s="10">
         <v>23191</v>
       </c>
-      <c r="H6" s="9">
-        <v>46235</v>
-      </c>
-      <c r="I6" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J6" s="1" t="s">
+      <c r="H6" s="13">
+        <v>46235</v>
+      </c>
+      <c r="I6" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" s="10" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1462,178 +1482,178 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="7" t="s">
+    <row r="12" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D12" s="1">
-        <v>33</v>
-      </c>
-      <c r="E12" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F12" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G12" s="1">
+      <c r="C12" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D12" s="10">
+        <v>33</v>
+      </c>
+      <c r="E12" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F12" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G12" s="10">
         <v>23619</v>
       </c>
-      <c r="H12" s="9">
-        <v>46235</v>
-      </c>
-      <c r="I12" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J12" s="1" t="s">
+      <c r="H12" s="13">
+        <v>46235</v>
+      </c>
+      <c r="I12" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J12" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="7" t="s">
+      <c r="K12" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D13" s="1">
-        <v>33</v>
-      </c>
-      <c r="E13" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F13" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G13" s="1">
+      <c r="C13" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D13" s="10">
+        <v>33</v>
+      </c>
+      <c r="E13" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F13" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G13" s="10">
         <v>22140</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="13">
         <v>46204</v>
       </c>
-      <c r="I13" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J13" s="1" t="s">
+      <c r="I13" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J13" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="7" t="s">
+      <c r="K13" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D14" s="1">
-        <v>33</v>
-      </c>
-      <c r="E14" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F14" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G14" s="1">
+      <c r="C14" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D14" s="10">
+        <v>33</v>
+      </c>
+      <c r="E14" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F14" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G14" s="10">
         <v>22583</v>
       </c>
-      <c r="H14" s="9">
-        <v>46235</v>
-      </c>
-      <c r="I14" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J14" s="1" t="s">
+      <c r="H14" s="13">
+        <v>46235</v>
+      </c>
+      <c r="I14" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J14" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="7" t="s">
+      <c r="K14" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D15" s="1">
-        <v>33</v>
-      </c>
-      <c r="E15" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F15" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G15" s="1">
+      <c r="C15" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D15" s="10">
+        <v>33</v>
+      </c>
+      <c r="E15" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F15" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G15" s="10">
         <v>23213</v>
       </c>
-      <c r="H15" s="9">
-        <v>46235</v>
-      </c>
-      <c r="I15" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J15" s="1" t="s">
+      <c r="H15" s="13">
+        <v>46235</v>
+      </c>
+      <c r="I15" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="7" t="s">
+      <c r="K15" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D16" s="1">
-        <v>33</v>
-      </c>
-      <c r="E16" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F16" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G16" s="1">
+      <c r="C16" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D16" s="10">
+        <v>33</v>
+      </c>
+      <c r="E16" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F16" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G16" s="10">
         <v>21381</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="13">
         <v>46204</v>
       </c>
-      <c r="I16" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J16" s="1" t="s">
+      <c r="I16" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J16" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" s="10" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1777,73 +1797,73 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="7" t="s">
+    <row r="21" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D21" s="1">
-        <v>33</v>
-      </c>
-      <c r="E21" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F21" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G21" s="1">
+      <c r="C21" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D21" s="10">
+        <v>33</v>
+      </c>
+      <c r="E21" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F21" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G21" s="10">
         <v>23318</v>
       </c>
-      <c r="H21" s="9">
-        <v>46235</v>
-      </c>
-      <c r="I21" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J21" s="1" t="s">
+      <c r="H21" s="13">
+        <v>46235</v>
+      </c>
+      <c r="I21" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="7" t="s">
+      <c r="K21" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D22" s="1">
-        <v>33</v>
-      </c>
-      <c r="E22" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F22" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G22" s="1">
+      <c r="C22" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D22" s="10">
+        <v>33</v>
+      </c>
+      <c r="E22" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F22" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G22" s="10">
         <v>22680</v>
       </c>
-      <c r="H22" s="9">
-        <v>46235</v>
-      </c>
-      <c r="I22" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J22" s="1" t="s">
+      <c r="H22" s="13">
+        <v>46235</v>
+      </c>
+      <c r="I22" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J22" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="K22" s="10" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2302,38 +2322,38 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B36" s="7" t="s">
+    <row r="36" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B36" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C36" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D36" s="1">
-        <v>33</v>
-      </c>
-      <c r="E36" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F36" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G36" s="1">
+      <c r="C36" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D36" s="10">
+        <v>33</v>
+      </c>
+      <c r="E36" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F36" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G36" s="10">
         <v>18258</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="13">
         <v>46174</v>
       </c>
-      <c r="I36" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J36" s="1" t="s">
+      <c r="I36" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J36" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="K36" s="10" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2407,38 +2427,38 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B39" s="7" t="s">
+    <row r="39" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C39" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D39" s="1">
-        <v>33</v>
-      </c>
-      <c r="E39" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F39" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G39" s="1">
+      <c r="C39" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D39" s="10">
+        <v>33</v>
+      </c>
+      <c r="E39" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F39" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G39" s="10">
         <v>22729</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="13">
         <v>46204</v>
       </c>
-      <c r="I39" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J39" s="1" t="s">
+      <c r="I39" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J39" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="K39" s="10" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2465,7 +2485,7 @@
       <c r="E46" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{7D4B4A2E-3296-414C-B792-C3952B38D84D}">
+  <autoFilter ref="A1:K39" xr:uid="{7D4B4A2E-3296-414C-B792-C3952B38D84D}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K42">
       <sortCondition ref="B1"/>
     </sortState>
@@ -2529,38 +2549,38 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="1">
-        <v>33</v>
-      </c>
-      <c r="E2" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F2" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G2" s="1">
+      <c r="C2" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="10">
+        <v>33</v>
+      </c>
+      <c r="E2" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F2" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G2" s="10">
         <v>22896</v>
       </c>
-      <c r="H2" s="9">
-        <v>46235</v>
-      </c>
-      <c r="I2" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="H2" s="13">
+        <v>46235</v>
+      </c>
+      <c r="I2" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="10" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2669,38 +2689,38 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="1">
-        <v>33</v>
-      </c>
-      <c r="E6" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F6" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="C6" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="10">
+        <v>33</v>
+      </c>
+      <c r="E6" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F6" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G6" s="10">
         <v>22961</v>
       </c>
-      <c r="H6" s="9">
-        <v>46235</v>
-      </c>
-      <c r="I6" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J6" s="1" t="s">
+      <c r="H6" s="13">
+        <v>46235</v>
+      </c>
+      <c r="I6" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" s="10" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2733,7 +2753,7 @@
         <v>46258</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>31</v>
@@ -2774,38 +2794,38 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D9" s="1">
-        <v>33</v>
-      </c>
-      <c r="E9" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F9" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G9" s="1">
+      <c r="C9" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D9" s="10">
+        <v>33</v>
+      </c>
+      <c r="E9" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F9" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G9" s="10">
         <v>23097</v>
       </c>
-      <c r="H9" s="9">
-        <v>46235</v>
-      </c>
-      <c r="I9" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J9" s="1" t="s">
+      <c r="H9" s="13">
+        <v>46235</v>
+      </c>
+      <c r="I9" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" s="10" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2908,7 +2928,7 @@
         <v>46258</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>31</v>
@@ -2984,143 +3004,143 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D15" s="1">
-        <v>33</v>
-      </c>
-      <c r="E15" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F15" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G15" s="1">
+      <c r="C15" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D15" s="10">
+        <v>33</v>
+      </c>
+      <c r="E15" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F15" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G15" s="10">
         <v>23348</v>
       </c>
-      <c r="H15" s="9">
-        <v>46235</v>
-      </c>
-      <c r="I15" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J15" s="1" t="s">
+      <c r="H15" s="13">
+        <v>46235</v>
+      </c>
+      <c r="I15" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J15" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K15" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:11" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D16" s="1">
-        <v>33</v>
-      </c>
-      <c r="E16" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F16" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G16" s="1">
+      <c r="C16" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D16" s="10">
+        <v>33</v>
+      </c>
+      <c r="E16" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F16" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G16" s="10">
         <v>23091</v>
       </c>
-      <c r="H16" s="9">
-        <v>46235</v>
-      </c>
-      <c r="I16" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J16" s="1" t="s">
+      <c r="H16" s="13">
+        <v>46235</v>
+      </c>
+      <c r="I16" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J16" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:11 16384:16384" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:11 16384:16384" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D17" s="1">
-        <v>33</v>
-      </c>
-      <c r="E17" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F17" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G17" s="1">
+      <c r="C17" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D17" s="10">
+        <v>33</v>
+      </c>
+      <c r="E17" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F17" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G17" s="10">
         <v>22908</v>
       </c>
-      <c r="H17" s="9">
-        <v>46235</v>
-      </c>
-      <c r="I17" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J17" s="1" t="s">
+      <c r="H17" s="13">
+        <v>46235</v>
+      </c>
+      <c r="I17" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J17" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="K17" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:11 16384:16384" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:11 16384:16384" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D18" s="1">
-        <v>33</v>
-      </c>
-      <c r="E18" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F18" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G18" s="1">
+      <c r="B18" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D18" s="10">
+        <v>33</v>
+      </c>
+      <c r="E18" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F18" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G18" s="10">
         <v>23024</v>
       </c>
-      <c r="H18" s="9">
-        <v>46235</v>
-      </c>
-      <c r="I18" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J18" s="1" t="s">
+      <c r="H18" s="13">
+        <v>46235</v>
+      </c>
+      <c r="I18" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J18" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="K18" s="10" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3264,38 +3284,38 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:11 16384:16384" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:11 16384:16384" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D23" s="1">
-        <v>33</v>
-      </c>
-      <c r="E23" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F23" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G23" s="1">
+      <c r="C23" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D23" s="10">
+        <v>33</v>
+      </c>
+      <c r="E23" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F23" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G23" s="10">
         <v>23349</v>
       </c>
-      <c r="H23" s="9">
-        <v>46235</v>
-      </c>
-      <c r="I23" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J23" s="1" t="s">
+      <c r="H23" s="13">
+        <v>46235</v>
+      </c>
+      <c r="I23" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J23" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="K23" s="10" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3334,38 +3354,38 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:11 16384:16384" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:11 16384:16384" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D25" s="1">
-        <v>33</v>
-      </c>
-      <c r="E25" s="8">
-        <v>46258</v>
-      </c>
-      <c r="F25" s="8">
-        <v>46262</v>
-      </c>
-      <c r="G25" s="1">
+      <c r="C25" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D25" s="10">
+        <v>33</v>
+      </c>
+      <c r="E25" s="12">
+        <v>46258</v>
+      </c>
+      <c r="F25" s="12">
+        <v>46262</v>
+      </c>
+      <c r="G25" s="10">
         <v>22659</v>
       </c>
-      <c r="H25" s="9">
-        <v>46235</v>
-      </c>
-      <c r="I25" s="8">
-        <v>46258</v>
-      </c>
-      <c r="J25" s="1" t="s">
+      <c r="H25" s="13">
+        <v>46235</v>
+      </c>
+      <c r="I25" s="12">
+        <v>46258</v>
+      </c>
+      <c r="J25" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K25" s="10" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3500,7 +3520,7 @@
       <c r="F41" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{150E6F24-F44A-4B31-BB13-245F81569AC3}">
+  <autoFilter ref="A1:K27" xr:uid="{150E6F24-F44A-4B31-BB13-245F81569AC3}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K28">
       <sortCondition ref="B1"/>
     </sortState>
